--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536130_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536130_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -558,67 +558,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6791</v>
+        <v>5.4607</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2583</v>
+        <v>4.62</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4208</v>
+        <v>0.8406</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6952</v>
+        <v>1.6969</v>
       </c>
       <c r="H2" t="n">
-        <v>2.512</v>
+        <v>-0.1144</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1832</v>
+        <v>1.8113</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1693</v>
+        <v>4.0619</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1288</v>
+        <v>1.5998</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0405</v>
+        <v>2.4621</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4741</v>
+        <v>-2.3651</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6168</v>
+        <v>-1.7142</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1427</v>
+        <v>-0.6509</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7549</v>
+        <v>2.5348</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7549</v>
+        <v>3.5097</v>
       </c>
       <c r="S2" t="n">
-        <v>0.229</v>
+        <v>0.619</v>
       </c>
       <c r="T2" t="n">
-        <v>0.089</v>
+        <v>0.313</v>
       </c>
       <c r="U2" t="n">
-        <v>0.14</v>
+        <v>0.306</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -641,67 +641,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2456</v>
+        <v>4.6791</v>
       </c>
       <c r="E3" t="n">
-        <v>3.405</v>
+        <v>3.2583</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8406</v>
+        <v>1.4208</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4818</v>
+        <v>2.6952</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1144</v>
+        <v>2.512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5962</v>
+        <v>0.1832</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8469</v>
+        <v>3.1693</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5998</v>
+        <v>3.1288</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2471</v>
+        <v>0.0405</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3651</v>
+        <v>-0.4741</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7142</v>
+        <v>-0.6168</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6509</v>
+        <v>0.1427</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5348</v>
+        <v>1.7549</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.5097</v>
+        <v>1.7549</v>
       </c>
       <c r="S3" t="n">
-        <v>0.619</v>
+        <v>0.229</v>
       </c>
       <c r="T3" t="n">
-        <v>0.313</v>
+        <v>0.089</v>
       </c>
       <c r="U3" t="n">
-        <v>0.306</v>
+        <v>0.14</v>
       </c>
       <c r="V3" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.61</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,67 +890,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.215</v>
+        <v>0.664</v>
       </c>
       <c r="E6" t="n">
-        <v>1.215</v>
+        <v>0.5579</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
       <c r="G6" t="n">
-        <v>1.215</v>
+        <v>-0.1926</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.1959</v>
       </c>
       <c r="I6" t="n">
-        <v>1.215</v>
+        <v>0.0033</v>
       </c>
       <c r="J6" t="n">
-        <v>1.215</v>
+        <v>0.2831</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.2831</v>
       </c>
       <c r="L6" t="n">
-        <v>1.215</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.4756</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.4789</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.0033</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.3301</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.2749</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.0553</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3315</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3315</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -973,67 +973,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.664</v>
+        <v>0.3959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5579</v>
+        <v>0.1371</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1061</v>
+        <v>0.2587</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1926</v>
+        <v>-2.7019</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1959</v>
+        <v>-0.8144</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0033</v>
+        <v>-1.8875</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2831</v>
+        <v>-0.865</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2831</v>
+        <v>0.4881</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-1.353</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4756</v>
+        <v>-1.837</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4789</v>
+        <v>-1.3024</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0033</v>
+        <v>-0.5345</v>
       </c>
       <c r="P7" t="n">
-        <v>0.195</v>
+        <v>0.7799</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R7" t="n">
-        <v>0.195</v>
+        <v>2.7298</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3301</v>
+        <v>0.4349</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2749</v>
+        <v>0.5118</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0553</v>
+        <v>-0.077</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3315</v>
+        <v>1.883</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.4401</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3315</v>
+        <v>-0.5571</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>M. BOTAS FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1056,67 +1056,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3959</v>
+        <v>-0.271</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1371</v>
+        <v>-2.0029</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2587</v>
+        <v>1.7319</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7019</v>
+        <v>3.4035</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8144</v>
+        <v>0.6914</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8875</v>
+        <v>2.7122</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.865</v>
+        <v>3.6778</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4881</v>
+        <v>2.3332</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.353</v>
+        <v>1.3446</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.837</v>
+        <v>-0.2742</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3024</v>
+        <v>-1.6418</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5345</v>
+        <v>1.3676</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7799</v>
+        <v>-3.7047</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9499</v>
+        <v>-5.8496</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7298</v>
+        <v>2.1448</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4349</v>
+        <v>0.6402</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5118</v>
+        <v>0.1689</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.077</v>
+        <v>0.4713</v>
       </c>
       <c r="V8" t="n">
-        <v>1.883</v>
+        <v>-0.61</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4401</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5571</v>
+        <v>-0.61</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. BOTAS FERNANDEZ</t>
+          <t>D. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1139,67 +1139,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.271</v>
+        <v>-0.9165</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0029</v>
+        <v>-1.3012</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7319</v>
+        <v>0.3847</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4035</v>
+        <v>-0.3206</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6914</v>
+        <v>-0.7289</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7122</v>
+        <v>0.4083</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6778</v>
+        <v>-0.66</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3332</v>
+        <v>-0.66</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3446</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2742</v>
+        <v>0.3394</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.6418</v>
+        <v>-0.0689</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3676</v>
+        <v>0.4083</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.7047</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5.8496</v>
+        <v>-0.9749</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1448</v>
+        <v>0.195</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6402</v>
+        <v>0.4626</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1689</v>
+        <v>0.3337</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4713</v>
+        <v>0.1289</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.61</v>
+        <v>-0.2786</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.61</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MELERO ZURITA</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1222,67 +1222,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9165</v>
+        <v>-2.1322</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3012</v>
+        <v>-0.4121</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3847</v>
+        <v>-1.72</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3206</v>
+        <v>-2.2464</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7289</v>
+        <v>0.6504</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4083</v>
+        <v>-2.8968</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.66</v>
+        <v>-0.6279</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.66</v>
+        <v>0.6521</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3394</v>
+        <v>-1.6185</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0689</v>
+        <v>-0.0017</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4083</v>
+        <v>-1.6168</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7799</v>
+        <v>0.9749</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.195</v>
+        <v>0.9749</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4626</v>
+        <v>0.0808</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3337</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1289</v>
+        <v>0.1436</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2786</v>
+        <v>-0.9415</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2786</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,67 +1305,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1322</v>
+        <v>-2.4188</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4121</v>
+        <v>-0.099</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.72</v>
+        <v>-2.3199</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.2464</v>
+        <v>-1.8747</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6504</v>
+        <v>-1.1913</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8968</v>
+        <v>-0.6834</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6279</v>
+        <v>0.5591</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6521</v>
+        <v>0.3161</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.28</v>
+        <v>0.243</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6185</v>
+        <v>-2.4338</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0017</v>
+        <v>-1.5075</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6168</v>
+        <v>-0.9264</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9749</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R11" t="n">
         <v>0.9749</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0808</v>
+        <v>0.2915</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.3168</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1436</v>
+        <v>-0.0253</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9415</v>
+        <v>-0.8357</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2786</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2201</v>
+        <v>-0.8357</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1376,7 +1376,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1388,67 +1388,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4188</v>
+        <v>-3.2813</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.099</v>
+        <v>-1.294</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3199</v>
+        <v>-1.9873</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8747</v>
+        <v>-3.6081</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1913</v>
+        <v>-1.9037</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6834</v>
+        <v>-1.7044</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5591</v>
+        <v>-1.4499</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3161</v>
+        <v>-1.3524</v>
       </c>
       <c r="L12" t="n">
-        <v>0.243</v>
+        <v>-0.0975</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4338</v>
+        <v>-2.1582</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5075</v>
+        <v>-0.5513</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.9264</v>
+        <v>-1.6069</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>1.5599</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9749</v>
+        <v>1.5599</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2915</v>
+        <v>-0.013</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3168</v>
+        <v>0.1559</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0253</v>
+        <v>-0.1689</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8357</v>
+        <v>-1.2201</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8357</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1471,157 +1471,157 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.2813</v>
+        <v>5.416100000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.294</v>
+        <v>7.3551</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9873</v>
+        <v>-1.9392</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6081</v>
+        <v>-6.4191</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.9037</v>
+        <v>-5.0908</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.7044</v>
+        <v>-1.3281</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.4499</v>
+        <v>7.7845</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3524</v>
+        <v>5.874899999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0975</v>
+        <v>1.9098</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.1582</v>
+        <v>-14.2036</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5513</v>
+        <v>-10.9656</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.6069</v>
+        <v>-3.238</v>
       </c>
       <c r="P13" t="n">
-        <v>1.5599</v>
+        <v>5.8496</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-12.674</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5599</v>
+        <v>18.5236</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.013</v>
+        <v>3.1082</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1559</v>
+        <v>2.2586</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1689</v>
+        <v>0.8496999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2201</v>
+        <v>2.8773</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>9.9862</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>play_by_play_2536130_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
+        <v>-7.108799999999999</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JAEN PARAISO INTERIOR FS</t>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.415999999999999</v>
+        <v>11.56</v>
       </c>
       <c r="E14" t="n">
-        <v>7.355099999999998</v>
+        <v>8.505800000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9392</v>
+        <v>3.0542</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.4192</v>
+        <v>7.6944</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.0908</v>
+        <v>1.775</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3282</v>
+        <v>5.9194</v>
       </c>
       <c r="J14" t="n">
-        <v>7.784500000000001</v>
+        <v>7.0799</v>
       </c>
       <c r="K14" t="n">
-        <v>5.874899999999999</v>
+        <v>1.7182</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9098</v>
+        <v>5.3618</v>
       </c>
       <c r="M14" t="n">
-        <v>-14.2036</v>
+        <v>0.6145</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.9656</v>
+        <v>0.0569</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.238</v>
+        <v>0.5576</v>
       </c>
       <c r="P14" t="n">
-        <v>5.849600000000001</v>
+        <v>2.1448</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.674</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>18.5236</v>
+        <v>2.1448</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1082</v>
+        <v>-0.1093</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2586</v>
+        <v>-0.4042</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8496999999999999</v>
+        <v>0.2949</v>
       </c>
       <c r="V14" t="n">
-        <v>2.8773</v>
+        <v>1.8301</v>
       </c>
       <c r="W14" t="n">
-        <v>9.9862</v>
+        <v>1.8301</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.108799999999999</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2536130_LIGAREGULARA_PROCESSED.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>A. BURGOS CABALLERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.56</v>
+        <v>7.0307</v>
       </c>
       <c r="E15" t="n">
-        <v>8.505800000000001</v>
+        <v>5.2831</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0542</v>
+        <v>1.7476</v>
       </c>
       <c r="G15" t="n">
-        <v>7.6944</v>
+        <v>4.7892</v>
       </c>
       <c r="H15" t="n">
-        <v>1.775</v>
+        <v>2.9681</v>
       </c>
       <c r="I15" t="n">
-        <v>5.9194</v>
+        <v>1.8211</v>
       </c>
       <c r="J15" t="n">
-        <v>7.0799</v>
+        <v>4.7798</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7182</v>
+        <v>2.7062</v>
       </c>
       <c r="L15" t="n">
-        <v>5.3618</v>
+        <v>2.0736</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6145</v>
+        <v>0.0094</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0569</v>
+        <v>0.2619</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5576</v>
+        <v>-0.2524</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1448</v>
+        <v>0.9749</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1448</v>
+        <v>1.9499</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1093</v>
+        <v>-0.285</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4042</v>
+        <v>-0.3519</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2949</v>
+        <v>0.0669</v>
       </c>
       <c r="V15" t="n">
-        <v>1.8301</v>
+        <v>1.5515</v>
       </c>
       <c r="W15" t="n">
         <v>1.8301</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. BURGOS CABALLERO</t>
+          <t>E. KALINICENKO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.0307</v>
+        <v>1.12</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2831</v>
+        <v>2.5998</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7476</v>
+        <v>-1.4798</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7892</v>
+        <v>1.1157</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9681</v>
+        <v>-0.762</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8211</v>
+        <v>1.8777</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7798</v>
+        <v>3.0067</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7062</v>
+        <v>-0.209</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0736</v>
+        <v>3.2156</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0094</v>
+        <v>-1.891</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2619</v>
+        <v>-0.553</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2524</v>
+        <v>-1.338</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9749</v>
+        <v>1.7549</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9499</v>
+        <v>1.7549</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.285</v>
+        <v>-0.2519</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3519</v>
+        <v>-0.4069</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0669</v>
+        <v>0.1549</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5515</v>
+        <v>-1.4986</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8301</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2786</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. KALINICENKO</t>
+          <t>V. ORLOV STURMAN MAURIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.12</v>
+        <v>0.3892</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5998</v>
+        <v>0.5808</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4798</v>
+        <v>-0.1916</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1157</v>
+        <v>1.1179</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.762</v>
+        <v>1.1372</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8777</v>
+        <v>-0.0193</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0067</v>
+        <v>2.6122</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.209</v>
+        <v>1.9642</v>
       </c>
       <c r="L17" t="n">
-        <v>3.2156</v>
+        <v>0.648</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.891</v>
+        <v>-1.4943</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.553</v>
+        <v>-0.8269</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.338</v>
+        <v>-0.6673</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7549</v>
+        <v>-2.3398</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.8997</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7549</v>
+        <v>1.5599</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2519</v>
+        <v>-0.1132</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4069</v>
+        <v>0.1441</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1549</v>
+        <v>-0.2572</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4986</v>
+        <v>1.7243</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.7243</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4986</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. ORLOV STURMAN MAURIN</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,64 +1882,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3892</v>
+        <v>-0.3166</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5808</v>
+        <v>-0.6139</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1916</v>
+        <v>0.2973</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1179</v>
+        <v>0.2729</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1372</v>
+        <v>-0.1048</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0193</v>
+        <v>0.3777</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6122</v>
+        <v>0.9472</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9642</v>
+        <v>0.5826</v>
       </c>
       <c r="L18" t="n">
-        <v>0.648</v>
+        <v>0.3645</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4943</v>
+        <v>-0.6742</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8269</v>
+        <v>-0.6874</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6673</v>
+        <v>0.0132</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3398</v>
+        <v>-1.3649</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8997</v>
+        <v>-1.9499</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5599</v>
+        <v>0.585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1132</v>
+        <v>0.7754</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1441</v>
+        <v>0.3888</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2572</v>
+        <v>0.3866</v>
       </c>
       <c r="V18" t="n">
-        <v>1.7243</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7243</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>J. SANTOS RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,58 +1965,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3166</v>
+        <v>-0.3734</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6139</v>
+        <v>0.123</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2973</v>
+        <v>-0.4964</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2729</v>
+        <v>0.5381</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1048</v>
+        <v>0.4943</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3777</v>
+        <v>0.0438</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9472</v>
+        <v>1.0861</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5826</v>
+        <v>1.0456</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3645</v>
+        <v>0.0405</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6742</v>
+        <v>-0.548</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6874</v>
+        <v>-0.5513</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0132</v>
+        <v>0.0033</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3649</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R19" t="n">
-        <v>0.585</v>
+        <v>0.195</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7754</v>
+        <v>-0.1315</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3888</v>
+        <v>0.0118</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3866</v>
+        <v>-0.1433</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SANTOS RODRIGUEZ</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3734</v>
+        <v>-0.5963000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>0.123</v>
+        <v>-0.0421</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4964</v>
+        <v>-0.5542</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5381</v>
+        <v>0.3269</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4943</v>
+        <v>-0.4977</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0438</v>
+        <v>0.8246</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0861</v>
+        <v>-0.283</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0456</v>
+        <v>-0.291</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>0.008</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.548</v>
+        <v>0.6099</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5513</v>
+        <v>-0.2067</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0033</v>
+        <v>0.8166</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7799</v>
+        <v>0.585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.195</v>
+        <v>0.585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1315</v>
+        <v>0.3219</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0118</v>
+        <v>0.2408</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1433</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.8301</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8301</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>K. NEWTON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5963000000000001</v>
+        <v>-1.4609</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0421</v>
+        <v>-3.2646</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5542</v>
+        <v>1.8038</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3269</v>
+        <v>-2.7849</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4977</v>
+        <v>2.9846</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8246</v>
+        <v>-5.7696</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.283</v>
+        <v>-2.2484</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.291</v>
+        <v>2.9932</v>
       </c>
       <c r="L21" t="n">
-        <v>0.008</v>
+        <v>-5.2416</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6099</v>
+        <v>-0.5365</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2067</v>
+        <v>-0.0086</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8166</v>
+        <v>-0.5279</v>
       </c>
       <c r="P21" t="n">
-        <v>0.585</v>
+        <v>-0.195</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R21" t="n">
-        <v>0.585</v>
+        <v>1.7549</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3219</v>
+        <v>0.299</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2408</v>
+        <v>-0.2865</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.5854</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8301</v>
+        <v>1.2201</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8301</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K. NEWTON</t>
+          <t>T. SAGNA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4609</v>
+        <v>-2.6015</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2646</v>
+        <v>-1.3625</v>
       </c>
       <c r="F22" t="n">
-        <v>1.8038</v>
+        <v>-1.239</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.7849</v>
+        <v>-0.8612</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9846</v>
+        <v>-0.4043</v>
       </c>
       <c r="I22" t="n">
-        <v>-5.7696</v>
+        <v>-0.4568</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.2484</v>
+        <v>0.0936</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9932</v>
+        <v>0.6931</v>
       </c>
       <c r="L22" t="n">
-        <v>-5.2416</v>
+        <v>-0.5995</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5365</v>
+        <v>-0.9547</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0086</v>
+        <v>-1.0974</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5279</v>
+        <v>0.1427</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.195</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7549</v>
+        <v>0.9749</v>
       </c>
       <c r="S22" t="n">
-        <v>0.299</v>
+        <v>0.229</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2865</v>
+        <v>-0.0104</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5854</v>
+        <v>0.2394</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2201</v>
+        <v>-0.9944</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2201</v>
+        <v>0.5042</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. SAGNA</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6015</v>
+        <v>-5.24</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3625</v>
+        <v>-3.3828</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.239</v>
+        <v>-1.8572</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8612</v>
+        <v>-1.2644</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4043</v>
+        <v>-0.9954</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4568</v>
+        <v>-0.2689</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0936</v>
+        <v>-0.377</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6931</v>
+        <v>0.3036</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5995</v>
+        <v>-0.6805</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9547</v>
+        <v>-0.8874</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0974</v>
+        <v>-1.299</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1427</v>
+        <v>0.4116</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9749</v>
+        <v>-2.5348</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9499</v>
+        <v>-2.9248</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9749</v>
+        <v>0.39</v>
       </c>
       <c r="S23" t="n">
-        <v>0.229</v>
+        <v>-0.2208</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0104</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2394</v>
+        <v>-0.1397</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9944</v>
+        <v>-1.2201</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5042</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4986</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>J. POTIER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.24</v>
+        <v>-11.6164</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3828</v>
+        <v>-6.4873</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.8572</v>
+        <v>-5.129</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.2644</v>
+        <v>-4.5256</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.9954</v>
+        <v>-1.504</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2689</v>
+        <v>-3.0216</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.377</v>
+        <v>-2.4935</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3036</v>
+        <v>-0.541</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6805</v>
+        <v>-1.9525</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8874</v>
+        <v>-2.0321</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.299</v>
+        <v>-0.963</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4116</v>
+        <v>-1.0691</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.5348</v>
+        <v>-3.1198</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9248</v>
+        <v>-3.8997</v>
       </c>
       <c r="R24" t="n">
-        <v>0.39</v>
+        <v>0.7799</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2208</v>
+        <v>-0.3108</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.08110000000000001</v>
+        <v>-0.0941</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1397</v>
+        <v>-0.2167</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.2201</v>
+        <v>-3.6602</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2201</v>
+        <v>-3.6602</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. POTIER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,152 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.6164</v>
+        <v>-2.105199999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.4873</v>
+        <v>1.939300000000004</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.129</v>
+        <v>-4.0443</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.5256</v>
+        <v>6.418999999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.504</v>
+        <v>5.090999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.0216</v>
+        <v>1.328100000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4935</v>
+        <v>14.2036</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.541</v>
+        <v>10.9657</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9525</v>
+        <v>3.2379</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.0321</v>
+        <v>-7.7844</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.963</v>
+        <v>-5.8745</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0691</v>
+        <v>-1.9097</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.1198</v>
+        <v>-5.849500000000001</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.8997</v>
+        <v>-18.5237</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7799</v>
+        <v>12.6742</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3108</v>
+        <v>0.2027999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0941</v>
+        <v>-0.8495999999999998</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2167</v>
+        <v>1.0523</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.6602</v>
+        <v>-2.8774</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>7.1088</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.6602</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536130_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-2.105199999999998</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1.939300000000004</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-4.0443</v>
-      </c>
-      <c r="G26" t="n">
-        <v>6.418999999999998</v>
-      </c>
-      <c r="H26" t="n">
-        <v>5.090999999999999</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.328100000000001</v>
-      </c>
-      <c r="J26" t="n">
-        <v>14.2036</v>
-      </c>
-      <c r="K26" t="n">
-        <v>10.9657</v>
-      </c>
-      <c r="L26" t="n">
-        <v>3.2379</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-7.7844</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-5.8745</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-1.9097</v>
-      </c>
-      <c r="P26" t="n">
-        <v>-5.849500000000001</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-18.5237</v>
-      </c>
-      <c r="R26" t="n">
-        <v>12.6742</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0.2027999999999999</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-0.8495999999999998</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.0523</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-2.8774</v>
-      </c>
-      <c r="W26" t="n">
-        <v>7.1088</v>
-      </c>
-      <c r="X26" t="n">
         <v>-9.9862</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
